--- a/artfynd/Björnbäcken artfynd.xlsx
+++ b/artfynd/Björnbäcken artfynd.xlsx
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88117040</v>
+        <v>88117134</v>
       </c>
       <c r="B4" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490177</v>
+        <v>490243</v>
       </c>
       <c r="R4" t="n">
-        <v>6914298</v>
+        <v>6914415</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,34 +978,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88117112</v>
+        <v>88117040</v>
       </c>
       <c r="B5" t="n">
-        <v>99038</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223597</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1013,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490230</v>
+        <v>490177</v>
       </c>
       <c r="R5" t="n">
-        <v>6914390</v>
+        <v>6914298</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1076,37 +1079,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>87526060</v>
+        <v>88117128</v>
       </c>
       <c r="B6" t="n">
-        <v>79327</v>
+        <v>99022</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1114,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490286</v>
+        <v>490244</v>
       </c>
       <c r="R6" t="n">
-        <v>6914843</v>
+        <v>6914413</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1144,12 +1148,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,37 +1181,34 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88117134</v>
+        <v>88117112</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>99038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1215,10 +1216,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490243</v>
+        <v>490230</v>
       </c>
       <c r="R7" t="n">
-        <v>6914415</v>
+        <v>6914390</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1278,32 +1279,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>87526069</v>
+        <v>87526060</v>
       </c>
       <c r="B8" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490301</v>
+        <v>490286</v>
       </c>
       <c r="R8" t="n">
-        <v>6914836</v>
+        <v>6914843</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1379,7 +1380,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>87526075</v>
+        <v>87526069</v>
       </c>
       <c r="B9" t="n">
         <v>80432</v>
@@ -1413,14 +1414,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Böråsflon, Hjd</t>
+          <t>Börsåsflon, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490307</v>
+        <v>490301</v>
       </c>
       <c r="R9" t="n">
-        <v>6914831</v>
+        <v>6914836</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1480,49 +1481,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>88117128</v>
+        <v>87526075</v>
       </c>
       <c r="B10" t="n">
-        <v>99022</v>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Börsåsflon, Hjd</t>
+          <t>Böråsflon, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490244</v>
+        <v>490307</v>
       </c>
       <c r="R10" t="n">
-        <v>6914413</v>
+        <v>6914831</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1549,12 +1549,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1883,7 +1883,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>87526019</v>
+        <v>87525968</v>
       </c>
       <c r="B14" t="n">
         <v>90932</v>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489956</v>
+        <v>489929</v>
       </c>
       <c r="R14" t="n">
-        <v>6915275</v>
+        <v>6915321</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110875633</v>
+        <v>87526019</v>
       </c>
       <c r="B15" t="n">
-        <v>93191</v>
+        <v>90932</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1995,34 +1995,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Halstjärnarna, Hjd</t>
+          <t>Börsåsflon, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489977</v>
+        <v>489956</v>
       </c>
       <c r="R15" t="n">
-        <v>6915261</v>
+        <v>6915275</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2049,12 +2052,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2070,60 +2073,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>87526008</v>
+        <v>110875633</v>
       </c>
       <c r="B16" t="n">
-        <v>79327</v>
+        <v>93191</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Börsåsflon, Hjd</t>
+          <t>Halstjärnarna, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489970</v>
+        <v>489977</v>
       </c>
       <c r="R16" t="n">
-        <v>6915290</v>
+        <v>6915261</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2150,12 +2150,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2171,44 +2171,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>87526021</v>
+        <v>87525985</v>
       </c>
       <c r="B17" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489956</v>
+        <v>489953</v>
       </c>
       <c r="R17" t="n">
-        <v>6915275</v>
+        <v>6915303</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2284,38 +2284,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>87526050</v>
+        <v>87526008</v>
       </c>
       <c r="B18" t="n">
-        <v>57141</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2323,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490014</v>
+        <v>489970</v>
       </c>
       <c r="R18" t="n">
-        <v>6915167</v>
+        <v>6915290</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2367,6 +2366,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2385,10 +2385,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>87526036</v>
+        <v>87525926</v>
       </c>
       <c r="B19" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2396,21 +2396,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489993</v>
+        <v>489905</v>
       </c>
       <c r="R19" t="n">
-        <v>6915215</v>
+        <v>6915354</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2486,10 +2486,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>87525968</v>
+        <v>87525976</v>
       </c>
       <c r="B20" t="n">
-        <v>90932</v>
+        <v>79946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2497,21 +2497,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489929</v>
+        <v>489946</v>
       </c>
       <c r="R20" t="n">
-        <v>6915321</v>
+        <v>6915308</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2587,32 +2587,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>87525985</v>
+        <v>87526021</v>
       </c>
       <c r="B21" t="n">
-        <v>79327</v>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2625,10 +2625,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489953</v>
+        <v>489956</v>
       </c>
       <c r="R21" t="n">
-        <v>6915303</v>
+        <v>6915275</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2688,37 +2688,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>87525926</v>
+        <v>87526050</v>
       </c>
       <c r="B22" t="n">
-        <v>79946</v>
+        <v>57141</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2726,10 +2727,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489905</v>
+        <v>490014</v>
       </c>
       <c r="R22" t="n">
-        <v>6915354</v>
+        <v>6915167</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2770,7 +2771,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2789,37 +2789,39 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>87525976</v>
+        <v>87525998</v>
       </c>
       <c r="B23" t="n">
-        <v>79946</v>
+        <v>5179</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2827,10 +2829,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489946</v>
+        <v>489955</v>
       </c>
       <c r="R23" t="n">
-        <v>6915308</v>
+        <v>6915304</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2863,6 +2865,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2020-08-17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2890,39 +2897,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>87525998</v>
+        <v>87526036</v>
       </c>
       <c r="B24" t="n">
-        <v>5179</v>
+        <v>79085</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2930,10 +2935,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489955</v>
+        <v>489993</v>
       </c>
       <c r="R24" t="n">
-        <v>6915304</v>
+        <v>6915215</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2966,11 +2971,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2020-08-17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3200,32 +3200,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>87526574</v>
+        <v>87526215</v>
       </c>
       <c r="B27" t="n">
-        <v>80433</v>
+        <v>91923</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490679</v>
+        <v>490759</v>
       </c>
       <c r="R27" t="n">
-        <v>6914332</v>
+        <v>6914410</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3301,7 +3301,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>87526582</v>
+        <v>87526574</v>
       </c>
       <c r="B28" t="n">
         <v>80433</v>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490675</v>
+        <v>490679</v>
       </c>
       <c r="R28" t="n">
-        <v>6914334</v>
+        <v>6914332</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3402,7 +3402,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>87526610</v>
+        <v>87526582</v>
       </c>
       <c r="B29" t="n">
         <v>80433</v>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490636</v>
+        <v>490675</v>
       </c>
       <c r="R29" t="n">
-        <v>6914332</v>
+        <v>6914334</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3503,7 +3503,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>87526635</v>
+        <v>87526610</v>
       </c>
       <c r="B30" t="n">
         <v>80433</v>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490610</v>
+        <v>490636</v>
       </c>
       <c r="R30" t="n">
-        <v>6914318</v>
+        <v>6914332</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3604,7 +3604,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>87526814</v>
+        <v>87526635</v>
       </c>
       <c r="B31" t="n">
         <v>80433</v>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490641</v>
+        <v>490610</v>
       </c>
       <c r="R31" t="n">
-        <v>6914337</v>
+        <v>6914318</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>87526224</v>
+        <v>87526814</v>
       </c>
       <c r="B32" t="n">
-        <v>79327</v>
+        <v>80433</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3743,10 +3743,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490757</v>
+        <v>490641</v>
       </c>
       <c r="R32" t="n">
-        <v>6914393</v>
+        <v>6914337</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3806,32 +3806,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>87526555</v>
+        <v>88117177</v>
       </c>
       <c r="B33" t="n">
-        <v>79327</v>
+        <v>92632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490705</v>
+        <v>490466</v>
       </c>
       <c r="R33" t="n">
-        <v>6914343</v>
+        <v>6914475</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3874,12 +3874,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3907,7 +3907,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>87526587</v>
+        <v>87526224</v>
       </c>
       <c r="B34" t="n">
         <v>79327</v>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490675</v>
+        <v>490757</v>
       </c>
       <c r="R34" t="n">
-        <v>6914334</v>
+        <v>6914393</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4008,32 +4008,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>87526566</v>
+        <v>87526555</v>
       </c>
       <c r="B35" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490690</v>
+        <v>490705</v>
       </c>
       <c r="R35" t="n">
-        <v>6914342</v>
+        <v>6914343</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4109,32 +4109,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>87526572</v>
+        <v>87526587</v>
       </c>
       <c r="B36" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4147,10 +4147,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490679</v>
+        <v>490675</v>
       </c>
       <c r="R36" t="n">
-        <v>6914332</v>
+        <v>6914334</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4210,32 +4210,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>87526584</v>
+        <v>87526791</v>
       </c>
       <c r="B37" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490675</v>
+        <v>490577</v>
       </c>
       <c r="R37" t="n">
-        <v>6914334</v>
+        <v>6914414</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4311,32 +4311,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>87526607</v>
+        <v>88117188</v>
       </c>
       <c r="B38" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490636</v>
+        <v>490477</v>
       </c>
       <c r="R38" t="n">
-        <v>6914332</v>
+        <v>6914478</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4412,7 +4412,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>87526622</v>
+        <v>87526566</v>
       </c>
       <c r="B39" t="n">
         <v>80432</v>
@@ -4450,10 +4450,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490624</v>
+        <v>490690</v>
       </c>
       <c r="R39" t="n">
-        <v>6914327</v>
+        <v>6914342</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4513,7 +4513,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>87526633</v>
+        <v>87526572</v>
       </c>
       <c r="B40" t="n">
         <v>80432</v>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490610</v>
+        <v>490679</v>
       </c>
       <c r="R40" t="n">
-        <v>6914318</v>
+        <v>6914332</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>87526739</v>
+        <v>87526584</v>
       </c>
       <c r="B41" t="n">
         <v>80432</v>
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490544</v>
+        <v>490675</v>
       </c>
       <c r="R41" t="n">
-        <v>6914324</v>
+        <v>6914334</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4715,7 +4715,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>87526748</v>
+        <v>87526607</v>
       </c>
       <c r="B42" t="n">
         <v>80432</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490541</v>
+        <v>490636</v>
       </c>
       <c r="R42" t="n">
-        <v>6914334</v>
+        <v>6914332</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4816,7 +4816,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>87526752</v>
+        <v>87526622</v>
       </c>
       <c r="B43" t="n">
         <v>80432</v>
@@ -4854,10 +4854,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490548</v>
+        <v>490624</v>
       </c>
       <c r="R43" t="n">
-        <v>6914350</v>
+        <v>6914327</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4917,7 +4917,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>87526758</v>
+        <v>87526633</v>
       </c>
       <c r="B44" t="n">
         <v>80432</v>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490559</v>
+        <v>490610</v>
       </c>
       <c r="R44" t="n">
-        <v>6914354</v>
+        <v>6914318</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5018,7 +5018,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>87526766</v>
+        <v>87526739</v>
       </c>
       <c r="B45" t="n">
         <v>80432</v>
@@ -5056,10 +5056,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490577</v>
+        <v>490544</v>
       </c>
       <c r="R45" t="n">
-        <v>6914358</v>
+        <v>6914324</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5119,7 +5119,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>87526783</v>
+        <v>87526748</v>
       </c>
       <c r="B46" t="n">
         <v>80432</v>
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490577</v>
+        <v>490541</v>
       </c>
       <c r="R46" t="n">
-        <v>6914395</v>
+        <v>6914334</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5220,7 +5220,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>87526813</v>
+        <v>87526752</v>
       </c>
       <c r="B47" t="n">
         <v>80432</v>
@@ -5258,10 +5258,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490641</v>
+        <v>490548</v>
       </c>
       <c r="R47" t="n">
-        <v>6914337</v>
+        <v>6914350</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5321,38 +5321,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>87526600</v>
+        <v>87526758</v>
       </c>
       <c r="B48" t="n">
-        <v>99022</v>
+        <v>80432</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5360,10 +5359,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490646</v>
+        <v>490559</v>
       </c>
       <c r="R48" t="n">
-        <v>6914341</v>
+        <v>6914354</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5423,42 +5422,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>87526237</v>
+        <v>87526766</v>
       </c>
       <c r="B49" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5466,10 +5460,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490757</v>
+        <v>490577</v>
       </c>
       <c r="R49" t="n">
-        <v>6914376</v>
+        <v>6914358</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5529,42 +5523,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>87526247</v>
+        <v>87526783</v>
       </c>
       <c r="B50" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5572,10 +5561,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490754</v>
+        <v>490577</v>
       </c>
       <c r="R50" t="n">
-        <v>6914372</v>
+        <v>6914395</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5635,42 +5624,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>88116971</v>
+        <v>87526813</v>
       </c>
       <c r="B51" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5678,10 +5662,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490415</v>
+        <v>490641</v>
       </c>
       <c r="R51" t="n">
-        <v>6914101</v>
+        <v>6914337</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5708,12 +5692,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5741,34 +5725,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>87526592</v>
+        <v>88117142</v>
       </c>
       <c r="B52" t="n">
-        <v>99038</v>
+        <v>80432</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>223597</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -5776,10 +5763,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490669</v>
+        <v>490378</v>
       </c>
       <c r="R52" t="n">
-        <v>6914343</v>
+        <v>6914437</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5806,12 +5793,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5839,32 +5826,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>87526215</v>
+        <v>88117157</v>
       </c>
       <c r="B53" t="n">
-        <v>91923</v>
+        <v>80432</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5877,10 +5864,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490759</v>
+        <v>490393</v>
       </c>
       <c r="R53" t="n">
-        <v>6914410</v>
+        <v>6914465</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5907,12 +5894,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5940,10 +5927,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>88117177</v>
+        <v>87526600</v>
       </c>
       <c r="B54" t="n">
-        <v>92632</v>
+        <v>99022</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5951,26 +5938,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3298</v>
+        <v>220093</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -5978,10 +5966,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490466</v>
+        <v>490646</v>
       </c>
       <c r="R54" t="n">
-        <v>6914475</v>
+        <v>6914341</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6008,12 +5996,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6041,10 +6029,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>87526133</v>
+        <v>87526237</v>
       </c>
       <c r="B55" t="n">
-        <v>79327</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6052,26 +6040,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6079,10 +6072,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490368</v>
+        <v>490757</v>
       </c>
       <c r="R55" t="n">
-        <v>6914789</v>
+        <v>6914376</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6142,10 +6135,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>87526151</v>
+        <v>87526247</v>
       </c>
       <c r="B56" t="n">
-        <v>79327</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6153,26 +6146,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6180,10 +6178,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490399</v>
+        <v>490754</v>
       </c>
       <c r="R56" t="n">
-        <v>6914799</v>
+        <v>6914372</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6243,10 +6241,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>87526791</v>
+        <v>88116971</v>
       </c>
       <c r="B57" t="n">
-        <v>79327</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6254,26 +6252,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6281,10 +6284,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490577</v>
+        <v>490415</v>
       </c>
       <c r="R57" t="n">
-        <v>6914414</v>
+        <v>6914101</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6311,12 +6314,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6344,37 +6347,34 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>88117188</v>
+        <v>87526592</v>
       </c>
       <c r="B58" t="n">
-        <v>79327</v>
+        <v>99038</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6382,10 +6382,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490477</v>
+        <v>490669</v>
       </c>
       <c r="R58" t="n">
-        <v>6914478</v>
+        <v>6914343</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6445,32 +6445,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>88117220</v>
+        <v>88117160</v>
       </c>
       <c r="B59" t="n">
-        <v>79327</v>
+        <v>80392</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6483,10 +6483,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490543</v>
+        <v>490393</v>
       </c>
       <c r="R59" t="n">
-        <v>6914516</v>
+        <v>6914465</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6546,32 +6546,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>87526181</v>
+        <v>87526133</v>
       </c>
       <c r="B60" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6584,10 +6584,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490413</v>
+        <v>490368</v>
       </c>
       <c r="R60" t="n">
-        <v>6914742</v>
+        <v>6914789</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6647,32 +6647,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>87526118</v>
+        <v>87526151</v>
       </c>
       <c r="B61" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6685,10 +6685,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490370</v>
+        <v>490399</v>
       </c>
       <c r="R61" t="n">
-        <v>6914777</v>
+        <v>6914799</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6748,32 +6748,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>87526126</v>
+        <v>88117220</v>
       </c>
       <c r="B62" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6786,10 +6786,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490368</v>
+        <v>490543</v>
       </c>
       <c r="R62" t="n">
-        <v>6914785</v>
+        <v>6914516</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6816,12 +6816,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6849,10 +6849,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>87526142</v>
+        <v>87526181</v>
       </c>
       <c r="B63" t="n">
-        <v>80432</v>
+        <v>79084</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6860,21 +6860,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>490363</v>
+        <v>490413</v>
       </c>
       <c r="R63" t="n">
-        <v>6914802</v>
+        <v>6914742</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6950,7 +6950,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>87526162</v>
+        <v>87526118</v>
       </c>
       <c r="B64" t="n">
         <v>80432</v>
@@ -6984,14 +6984,14 @@
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Böråsflon, Hjd</t>
+          <t>Börsåsflon, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>490398</v>
+        <v>490370</v>
       </c>
       <c r="R64" t="n">
-        <v>6914779</v>
+        <v>6914777</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7051,7 +7051,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>87526171</v>
+        <v>87526126</v>
       </c>
       <c r="B65" t="n">
         <v>80432</v>
@@ -7089,10 +7089,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>490394</v>
+        <v>490368</v>
       </c>
       <c r="R65" t="n">
-        <v>6914762</v>
+        <v>6914785</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7152,7 +7152,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>87526179</v>
+        <v>87526142</v>
       </c>
       <c r="B66" t="n">
         <v>80432</v>
@@ -7190,10 +7190,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>490413</v>
+        <v>490363</v>
       </c>
       <c r="R66" t="n">
-        <v>6914742</v>
+        <v>6914802</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7253,7 +7253,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>87526191</v>
+        <v>87526162</v>
       </c>
       <c r="B67" t="n">
         <v>80432</v>
@@ -7287,14 +7287,14 @@
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Börsåsflon, Hjd</t>
+          <t>Böråsflon, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>490501</v>
+        <v>490398</v>
       </c>
       <c r="R67" t="n">
-        <v>6914636</v>
+        <v>6914779</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7354,7 +7354,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>88117142</v>
+        <v>87526171</v>
       </c>
       <c r="B68" t="n">
         <v>80432</v>
@@ -7392,10 +7392,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490378</v>
+        <v>490394</v>
       </c>
       <c r="R68" t="n">
-        <v>6914437</v>
+        <v>6914762</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7422,12 +7422,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7455,7 +7455,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>88117157</v>
+        <v>87526179</v>
       </c>
       <c r="B69" t="n">
         <v>80432</v>
@@ -7493,10 +7493,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490393</v>
+        <v>490413</v>
       </c>
       <c r="R69" t="n">
-        <v>6914465</v>
+        <v>6914742</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7523,12 +7523,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7556,32 +7556,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>87526120</v>
+        <v>87526191</v>
       </c>
       <c r="B70" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7594,10 +7594,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490370</v>
+        <v>490501</v>
       </c>
       <c r="R70" t="n">
-        <v>6914777</v>
+        <v>6914636</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7657,10 +7657,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>88117200</v>
+        <v>87526120</v>
       </c>
       <c r="B71" t="n">
-        <v>99022</v>
+        <v>80461</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7668,27 +7668,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220093</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7696,10 +7695,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490493</v>
+        <v>490370</v>
       </c>
       <c r="R71" t="n">
-        <v>6914492</v>
+        <v>6914777</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7726,12 +7725,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7759,7 +7758,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>88117210</v>
+        <v>88117200</v>
       </c>
       <c r="B72" t="n">
         <v>99022</v>
@@ -7798,10 +7797,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>490496</v>
+        <v>490493</v>
       </c>
       <c r="R72" t="n">
-        <v>6914493</v>
+        <v>6914492</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7861,32 +7860,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>88117262</v>
+        <v>88117210</v>
       </c>
       <c r="B73" t="n">
-        <v>99118</v>
+        <v>99022</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7900,13 +7899,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490505</v>
+        <v>490496</v>
       </c>
       <c r="R73" t="n">
-        <v>6914501</v>
+        <v>6914493</v>
       </c>
       <c r="S73" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7963,32 +7962,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>87526193</v>
+        <v>88117262</v>
       </c>
       <c r="B74" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8002,13 +8001,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490501</v>
+        <v>490505</v>
       </c>
       <c r="R74" t="n">
-        <v>6914636</v>
+        <v>6914501</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8032,12 +8031,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8065,10 +8064,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>88117160</v>
+        <v>87526193</v>
       </c>
       <c r="B75" t="n">
-        <v>80392</v>
+        <v>97983</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8076,26 +8075,27 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -8103,10 +8103,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490393</v>
+        <v>490501</v>
       </c>
       <c r="R75" t="n">
-        <v>6914465</v>
+        <v>6914636</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8133,12 +8133,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="AD75" t="b">
